--- a/manual-testing-saucedemo/test-execution/Test-Execution-Report.xlsx
+++ b/manual-testing-saucedemo/test-execution/Test-Execution-Report.xlsx
@@ -1,21 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sony\Desktop\Mannual Testing\manual-testing-saucedemo\test-execution\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F68FCB5-4066-4723-9E78-A72E8A1EE521}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Test Scenarios" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Login" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Product" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Cart" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Checkout" sheetId="5" r:id="rId9"/>
+    <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="2" r:id="rId2"/>
+    <sheet name="Product" sheetId="3" r:id="rId3"/>
+    <sheet name="Cart" sheetId="4" r:id="rId4"/>
+    <sheet name="Checkout" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="179">
   <si>
     <t>Project Name</t>
   </si>
@@ -36,9 +45,6 @@
   </si>
   <si>
     <t>Created By</t>
-  </si>
-  <si>
-    <t>Prasadi Nishshanka</t>
   </si>
   <si>
     <t>Created Date</t>
@@ -606,29 +612,35 @@
   <si>
     <t>Order confirmation message displayed successfully</t>
   </si>
+  <si>
+    <t>Muskan Jain</t>
+  </si>
+  <si>
+    <t>21/6/2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-  </numFmts>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="5">
@@ -636,7 +648,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -658,7 +670,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -672,81 +690,59 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -754,7 +750,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -944,21 +940,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.13"/>
-    <col customWidth="1" min="2" max="2" width="34.13"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -966,7 +965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -974,7 +973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -982,189 +981,190 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3">
-        <v>46150.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="4"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="4"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="2">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z10"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="16.63"/>
-    <col customWidth="1" min="3" max="3" width="26.38"/>
-    <col customWidth="1" min="4" max="4" width="26.25"/>
-    <col customWidth="1" min="5" max="5" width="20.25"/>
-    <col customWidth="1" min="6" max="6" width="13.25"/>
-    <col customWidth="1" min="7" max="7" width="46.63"/>
-    <col customWidth="1" min="8" max="8" width="69.38"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="46.5703125" customWidth="1"/>
+    <col min="8" max="8" width="69.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="K3" s="10"/>
       <c r="L3" s="11"/>
@@ -1183,34 +1183,34 @@
       <c r="Y3" s="11"/>
       <c r="Z3" s="11"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="F4" s="10"/>
       <c r="G4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="I4" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" s="10"/>
       <c r="L4" s="11"/>
@@ -1229,34 +1229,34 @@
       <c r="Y4" s="11"/>
       <c r="Z4" s="11"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>50</v>
       </c>
       <c r="F5" s="10"/>
       <c r="G5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="I5" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="11"/>
@@ -1275,34 +1275,34 @@
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="F6" s="10"/>
       <c r="G6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="I6" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="11"/>
@@ -1321,34 +1321,34 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="I7" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="11"/>
@@ -1367,34 +1367,34 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="11"/>
@@ -1413,36 +1413,36 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="I9" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="11"/>
@@ -1461,34 +1461,34 @@
       <c r="Y9" s="11"/>
       <c r="Z9" s="11"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="I10" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K10" s="10"/>
       <c r="L10" s="11"/>
@@ -1509,797 +1509,800 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink display="&lt;&lt;Test Scenarios" location="'Test Scenarios'!A1" ref="A2"/>
+    <hyperlink ref="A2" location="'Test Scenarios'!A1" display="&lt;&lt;Test Scenarios" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="16.63"/>
-    <col customWidth="1" min="3" max="3" width="38.0"/>
-    <col customWidth="1" min="4" max="4" width="26.25"/>
-    <col customWidth="1" min="5" max="5" width="25.63"/>
-    <col customWidth="1" min="6" max="6" width="13.25"/>
-    <col customWidth="1" min="7" max="7" width="46.63"/>
-    <col customWidth="1" min="8" max="8" width="33.63"/>
-    <col customWidth="1" min="11" max="11" width="13.25"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="46.5703125" customWidth="1"/>
+    <col min="8" max="8" width="33.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="10"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" s="10"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="B6" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="I6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="B7" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="I8" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K8" s="10"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="I9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="10"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="s">
+      <c r="B10" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="12" t="s">
+      <c r="D10" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="14" t="s">
+      <c r="F10" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="G10" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="H10" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="I10" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="J10" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="K10" s="12" t="s">
         <v>122</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink display="&lt;&lt;Test Scenarios" location="'Test Scenarios'!A1" ref="A2"/>
+    <hyperlink ref="A2" location="'Test Scenarios'!A1" display="&lt;&lt;Test Scenarios" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="16.63"/>
-    <col customWidth="1" min="3" max="3" width="35.13"/>
-    <col customWidth="1" min="4" max="4" width="26.25"/>
-    <col customWidth="1" min="5" max="5" width="25.63"/>
-    <col customWidth="1" min="7" max="7" width="46.63"/>
-    <col customWidth="1" min="8" max="8" width="35.13"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="7" max="7" width="46.5703125" customWidth="1"/>
+    <col min="8" max="8" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="F3" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="H3" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="I3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="I3" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="12" t="s">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" s="10"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="B6" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="I6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="B7" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>156</v>
-      </c>
       <c r="I8" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K8" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink display="&lt;&lt;Test Scenarios" location="'Test Scenarios'!A1" ref="A2"/>
+    <hyperlink ref="A2" location="'Test Scenarios'!A1" display="&lt;&lt;Test Scenarios" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="16.63"/>
-    <col customWidth="1" min="3" max="3" width="29.63"/>
-    <col customWidth="1" min="4" max="4" width="26.25"/>
-    <col customWidth="1" min="5" max="5" width="25.63"/>
-    <col customWidth="1" min="7" max="7" width="46.63"/>
-    <col customWidth="1" min="8" max="8" width="44.75"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="7" max="7" width="46.5703125" customWidth="1"/>
+    <col min="8" max="8" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="10"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" s="10"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="B6" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>177</v>
-      </c>
       <c r="I6" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K6" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink display="&lt;&lt;Test Scenarios" location="'Test Scenarios'!A1" ref="A2"/>
+    <hyperlink ref="A2" location="'Test Scenarios'!A1" display="&lt;&lt;Test Scenarios" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>